--- a/dashboard_261006.xlsx
+++ b/dashboard_261006.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IUH\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1929BBAF-6734-44B7-B7C5-EED9FCB7DF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82DC1BE-BC92-492C-BF82-D8CA266E8730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{76034374-3134-4196-BC82-9585DD782D15}"/>
   </bookViews>
@@ -11183,7 +11183,7 @@
     </row>
     <row r="132" spans="1:13" ht="32.1" customHeight="1">
       <c r="A132" s="9" t="str">
-        <f t="shared" ref="A132:A153" si="2">CONCATENATE("25-",ROW()-ROW($A$2))</f>
+        <f t="shared" ref="A132:A154" si="2">CONCATENATE("25-",ROW()-ROW($A$2))</f>
         <v>25-130</v>
       </c>
       <c r="B132" s="9" t="s">
@@ -11985,9 +11985,9 @@
       <c r="M153" s="45"/>
     </row>
     <row r="154" spans="1:15" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A154" s="9">
-        <f t="shared" ref="A154:A217" si="3">ROW()-ROW($A$8)</f>
-        <v>146</v>
+      <c r="A154" s="9" t="str">
+        <f>CONCATENATE("26-",ROW()-ROW($A$153))</f>
+        <v>26-1</v>
       </c>
       <c r="B154" s="9" t="s">
         <v>86</v>
@@ -12033,9 +12033,9 @@
       </c>
     </row>
     <row r="155" spans="1:15" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A155" s="9">
-        <f t="shared" si="3"/>
-        <v>147</v>
+      <c r="A155" s="9" t="str">
+        <f t="shared" ref="A155:A218" si="3">CONCATENATE("26-",ROW()-ROW($A$153))</f>
+        <v>26-2</v>
       </c>
       <c r="B155" s="9" t="s">
         <v>86</v>
@@ -12075,9 +12075,9 @@
       <c r="O155" s="142"/>
     </row>
     <row r="156" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A156" s="9">
+      <c r="A156" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>148</v>
+        <v>26-3</v>
       </c>
       <c r="B156" s="9" t="s">
         <v>185</v>
@@ -12115,9 +12115,9 @@
       <c r="O156" s="142"/>
     </row>
     <row r="157" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A157" s="9">
+      <c r="A157" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>149</v>
+        <v>26-4</v>
       </c>
       <c r="B157" s="9" t="s">
         <v>86</v>
@@ -12159,9 +12159,9 @@
       <c r="O157" s="142"/>
     </row>
     <row r="158" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A158" s="9">
+      <c r="A158" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>150</v>
+        <v>26-5</v>
       </c>
       <c r="B158" s="9" t="s">
         <v>86</v>
@@ -12203,9 +12203,9 @@
       <c r="O158" s="142"/>
     </row>
     <row r="159" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A159" s="9">
+      <c r="A159" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>151</v>
+        <v>26-6</v>
       </c>
       <c r="B159" s="9" t="s">
         <v>86</v>
@@ -12247,9 +12247,9 @@
       <c r="O159" s="142"/>
     </row>
     <row r="160" spans="1:15" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A160" s="9">
+      <c r="A160" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>152</v>
+        <v>26-7</v>
       </c>
       <c r="B160" s="9" t="s">
         <v>86</v>
@@ -12291,9 +12291,9 @@
       <c r="O160" s="142"/>
     </row>
     <row r="161" spans="1:15" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A161" s="9">
+      <c r="A161" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>153</v>
+        <v>26-8</v>
       </c>
       <c r="B161" s="9" t="s">
         <v>86</v>
@@ -12335,9 +12335,9 @@
       <c r="O161" s="142"/>
     </row>
     <row r="162" spans="1:15" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A162" s="9">
+      <c r="A162" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>154</v>
+        <v>26-9</v>
       </c>
       <c r="B162" s="9" t="s">
         <v>86</v>
@@ -12379,9 +12379,9 @@
       <c r="O162" s="142"/>
     </row>
     <row r="163" spans="1:15" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A163" s="9">
+      <c r="A163" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>155</v>
+        <v>26-10</v>
       </c>
       <c r="B163" s="9" t="s">
         <v>86</v>
@@ -12423,9 +12423,9 @@
       <c r="O163" s="142"/>
     </row>
     <row r="164" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A164" s="9">
+      <c r="A164" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>156</v>
+        <v>26-11</v>
       </c>
       <c r="B164" s="9" t="s">
         <v>86</v>
@@ -12467,9 +12467,9 @@
       <c r="O164" s="142"/>
     </row>
     <row r="165" spans="1:15" s="40" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A165" s="9">
+      <c r="A165" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>157</v>
+        <v>26-12</v>
       </c>
       <c r="B165" s="9" t="s">
         <v>86</v>
@@ -12511,9 +12511,9 @@
       <c r="O165" s="142"/>
     </row>
     <row r="166" spans="1:15" s="42" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A166" s="9">
+      <c r="A166" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>158</v>
+        <v>26-13</v>
       </c>
       <c r="B166" s="9" t="s">
         <v>86</v>
@@ -12555,9 +12555,9 @@
       <c r="O166" s="142"/>
     </row>
     <row r="167" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A167" s="9">
+      <c r="A167" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>159</v>
+        <v>26-14</v>
       </c>
       <c r="B167" s="9" t="s">
         <v>86</v>
@@ -12597,9 +12597,9 @@
       <c r="O167" s="142"/>
     </row>
     <row r="168" spans="1:15" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A168" s="9">
+      <c r="A168" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>160</v>
+        <v>26-15</v>
       </c>
       <c r="B168" s="9" t="s">
         <v>86</v>
@@ -12639,9 +12639,9 @@
       <c r="O168" s="142"/>
     </row>
     <row r="169" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A169" s="9">
+      <c r="A169" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>161</v>
+        <v>26-16</v>
       </c>
       <c r="B169" s="9" t="s">
         <v>86</v>
@@ -12681,9 +12681,9 @@
       <c r="O169" s="142"/>
     </row>
     <row r="170" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A170" s="9">
+      <c r="A170" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>162</v>
+        <v>26-17</v>
       </c>
       <c r="B170" s="9" t="s">
         <v>86</v>
@@ -12725,9 +12725,9 @@
       </c>
     </row>
     <row r="171" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A171" s="9">
+      <c r="A171" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>163</v>
+        <v>26-18</v>
       </c>
       <c r="B171" s="9" t="s">
         <v>17</v>
@@ -12767,9 +12767,9 @@
       <c r="O171" s="142"/>
     </row>
     <row r="172" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A172" s="9">
+      <c r="A172" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>164</v>
+        <v>26-19</v>
       </c>
       <c r="B172" s="9" t="s">
         <v>17</v>
@@ -12809,9 +12809,9 @@
       <c r="O172" s="142"/>
     </row>
     <row r="173" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A173" s="9">
+      <c r="A173" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>165</v>
+        <v>26-20</v>
       </c>
       <c r="B173" s="9" t="s">
         <v>329</v>
@@ -12847,9 +12847,9 @@
       <c r="O173" s="142"/>
     </row>
     <row r="174" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A174" s="9">
+      <c r="A174" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>166</v>
+        <v>26-21</v>
       </c>
       <c r="B174" s="9" t="s">
         <v>333</v>
@@ -12885,9 +12885,9 @@
       <c r="O174" s="142"/>
     </row>
     <row r="175" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A175" s="9">
+      <c r="A175" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>167</v>
+        <v>26-22</v>
       </c>
       <c r="B175" s="9" t="s">
         <v>329</v>
@@ -12923,9 +12923,9 @@
       <c r="O175" s="142"/>
     </row>
     <row r="176" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A176" s="9">
+      <c r="A176" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>168</v>
+        <v>26-23</v>
       </c>
       <c r="B176" s="9" t="s">
         <v>86</v>
@@ -12965,9 +12965,9 @@
       <c r="O176" s="142"/>
     </row>
     <row r="177" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A177" s="9">
+      <c r="A177" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>169</v>
+        <v>26-24</v>
       </c>
       <c r="B177" s="9" t="s">
         <v>17</v>
@@ -13007,9 +13007,9 @@
       <c r="O177" s="142"/>
     </row>
     <row r="178" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A178" s="9">
+      <c r="A178" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>170</v>
+        <v>26-25</v>
       </c>
       <c r="B178" s="9" t="s">
         <v>17</v>
@@ -13049,9 +13049,9 @@
       <c r="O178" s="142"/>
     </row>
     <row r="179" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A179" s="9">
+      <c r="A179" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>171</v>
+        <v>26-26</v>
       </c>
       <c r="B179" s="9" t="s">
         <v>86</v>
@@ -13091,9 +13091,9 @@
       <c r="O179" s="142"/>
     </row>
     <row r="180" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A180" s="9">
+      <c r="A180" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>172</v>
+        <v>26-27</v>
       </c>
       <c r="B180" s="9" t="s">
         <v>17</v>
@@ -13133,9 +13133,9 @@
       <c r="O180" s="142"/>
     </row>
     <row r="181" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A181" s="9">
+      <c r="A181" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>173</v>
+        <v>26-28</v>
       </c>
       <c r="B181" s="9" t="s">
         <v>185</v>
@@ -13171,9 +13171,9 @@
       <c r="O181" s="142"/>
     </row>
     <row r="182" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A182" s="9">
+      <c r="A182" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>174</v>
+        <v>26-29</v>
       </c>
       <c r="B182" s="9" t="s">
         <v>86</v>
@@ -13213,9 +13213,9 @@
       <c r="O182" s="142"/>
     </row>
     <row r="183" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A183" s="9">
+      <c r="A183" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>175</v>
+        <v>26-30</v>
       </c>
       <c r="B183" s="9" t="s">
         <v>17</v>
@@ -13255,9 +13255,9 @@
       <c r="O183" s="142"/>
     </row>
     <row r="184" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A184" s="9">
+      <c r="A184" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>176</v>
+        <v>26-31</v>
       </c>
       <c r="B184" s="9" t="s">
         <v>17</v>
@@ -13297,9 +13297,9 @@
       <c r="O184" s="142"/>
     </row>
     <row r="185" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A185" s="9">
+      <c r="A185" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>177</v>
+        <v>26-32</v>
       </c>
       <c r="B185" s="9" t="s">
         <v>17</v>
@@ -13339,9 +13339,9 @@
       <c r="O185" s="142"/>
     </row>
     <row r="186" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A186" s="9">
+      <c r="A186" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>178</v>
+        <v>26-33</v>
       </c>
       <c r="B186" s="9" t="s">
         <v>185</v>
@@ -13377,9 +13377,9 @@
       <c r="O186" s="142"/>
     </row>
     <row r="187" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A187" s="9">
+      <c r="A187" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>179</v>
+        <v>26-34</v>
       </c>
       <c r="B187" s="9" t="s">
         <v>86</v>
@@ -13419,9 +13419,9 @@
       <c r="O187" s="142"/>
     </row>
     <row r="188" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A188" s="9">
+      <c r="A188" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>180</v>
+        <v>26-35</v>
       </c>
       <c r="B188" s="9" t="s">
         <v>185</v>
@@ -13457,9 +13457,9 @@
       <c r="O188" s="142"/>
     </row>
     <row r="189" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A189" s="9">
+      <c r="A189" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>181</v>
+        <v>26-36</v>
       </c>
       <c r="B189" s="9" t="s">
         <v>185</v>
@@ -13495,9 +13495,9 @@
       <c r="O189" s="142"/>
     </row>
     <row r="190" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A190" s="9">
+      <c r="A190" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>182</v>
+        <v>26-37</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>17</v>
@@ -13537,9 +13537,9 @@
       <c r="O190" s="142"/>
     </row>
     <row r="191" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A191" s="9">
+      <c r="A191" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>183</v>
+        <v>26-38</v>
       </c>
       <c r="B191" s="9" t="s">
         <v>17</v>
@@ -13579,9 +13579,9 @@
       <c r="O191" s="142"/>
     </row>
     <row r="192" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A192" s="9">
+      <c r="A192" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>184</v>
+        <v>26-39</v>
       </c>
       <c r="B192" s="9" t="s">
         <v>185</v>
@@ -13617,9 +13617,9 @@
       <c r="O192" s="142"/>
     </row>
     <row r="193" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A193" s="9">
+      <c r="A193" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>185</v>
+        <v>26-40</v>
       </c>
       <c r="B193" s="9" t="s">
         <v>185</v>
@@ -13655,9 +13655,9 @@
       <c r="O193" s="142"/>
     </row>
     <row r="194" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A194" s="9">
+      <c r="A194" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>186</v>
+        <v>26-41</v>
       </c>
       <c r="B194" s="9" t="s">
         <v>17</v>
@@ -13697,9 +13697,9 @@
       <c r="O194" s="142"/>
     </row>
     <row r="195" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A195" s="9">
+      <c r="A195" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>187</v>
+        <v>26-42</v>
       </c>
       <c r="B195" s="9" t="s">
         <v>185</v>
@@ -13739,9 +13739,9 @@
       <c r="O195" s="142"/>
     </row>
     <row r="196" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A196" s="9">
+      <c r="A196" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>188</v>
+        <v>26-43</v>
       </c>
       <c r="B196" s="9" t="s">
         <v>17</v>
@@ -13781,9 +13781,9 @@
       <c r="O196" s="142"/>
     </row>
     <row r="197" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A197" s="9">
+      <c r="A197" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>189</v>
+        <v>26-44</v>
       </c>
       <c r="B197" s="9" t="s">
         <v>17</v>
@@ -13823,9 +13823,9 @@
       <c r="O197" s="142"/>
     </row>
     <row r="198" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A198" s="9">
+      <c r="A198" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>190</v>
+        <v>26-45</v>
       </c>
       <c r="B198" s="9" t="s">
         <v>185</v>
@@ -13861,9 +13861,9 @@
       <c r="O198" s="142"/>
     </row>
     <row r="199" spans="1:15" s="71" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A199" s="9">
+      <c r="A199" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>191</v>
+        <v>26-46</v>
       </c>
       <c r="B199" s="9" t="s">
         <v>86</v>
@@ -13903,9 +13903,9 @@
       <c r="O199" s="142"/>
     </row>
     <row r="200" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A200" s="9">
+      <c r="A200" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>192</v>
+        <v>26-47</v>
       </c>
       <c r="B200" s="9" t="s">
         <v>86</v>
@@ -13947,9 +13947,9 @@
       </c>
     </row>
     <row r="201" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A201" s="9">
+      <c r="A201" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>193</v>
+        <v>26-48</v>
       </c>
       <c r="B201" s="9" t="s">
         <v>17</v>
@@ -13991,9 +13991,9 @@
       </c>
     </row>
     <row r="202" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A202" s="9">
+      <c r="A202" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>194</v>
+        <v>26-49</v>
       </c>
       <c r="B202" s="9" t="s">
         <v>17</v>
@@ -14035,9 +14035,9 @@
       </c>
     </row>
     <row r="203" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A203" s="9">
+      <c r="A203" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>195</v>
+        <v>26-50</v>
       </c>
       <c r="B203" s="9" t="s">
         <v>17</v>
@@ -14079,9 +14079,9 @@
       </c>
     </row>
     <row r="204" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A204" s="9">
+      <c r="A204" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>196</v>
+        <v>26-51</v>
       </c>
       <c r="B204" s="9" t="s">
         <v>17</v>
@@ -14123,9 +14123,9 @@
       </c>
     </row>
     <row r="205" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A205" s="9">
+      <c r="A205" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>197</v>
+        <v>26-52</v>
       </c>
       <c r="B205" s="9" t="s">
         <v>329</v>
@@ -14163,9 +14163,9 @@
       </c>
     </row>
     <row r="206" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A206" s="9">
+      <c r="A206" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>198</v>
+        <v>26-53</v>
       </c>
       <c r="B206" s="9" t="s">
         <v>185</v>
@@ -14203,9 +14203,9 @@
       <c r="O206" s="142"/>
     </row>
     <row r="207" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A207" s="9">
+      <c r="A207" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>199</v>
+        <v>26-54</v>
       </c>
       <c r="B207" s="9" t="s">
         <v>17</v>
@@ -14247,9 +14247,9 @@
       <c r="O207" s="142"/>
     </row>
     <row r="208" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A208" s="9">
+      <c r="A208" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>26-55</v>
       </c>
       <c r="B208" s="9" t="s">
         <v>17</v>
@@ -14289,9 +14289,9 @@
       <c r="O208" s="142"/>
     </row>
     <row r="209" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A209" s="9">
+      <c r="A209" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>201</v>
+        <v>26-56</v>
       </c>
       <c r="B209" s="9" t="s">
         <v>17</v>
@@ -14335,9 +14335,9 @@
       </c>
     </row>
     <row r="210" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A210" s="9">
+      <c r="A210" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>202</v>
+        <v>26-57</v>
       </c>
       <c r="B210" s="9" t="s">
         <v>17</v>
@@ -14377,9 +14377,9 @@
       <c r="O210" s="142"/>
     </row>
     <row r="211" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A211" s="9">
+      <c r="A211" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>203</v>
+        <v>26-58</v>
       </c>
       <c r="B211" s="9" t="s">
         <v>86</v>
@@ -14419,9 +14419,9 @@
       <c r="O211" s="142"/>
     </row>
     <row r="212" spans="1:15" s="42" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A212" s="9">
+      <c r="A212" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>204</v>
+        <v>26-59</v>
       </c>
       <c r="B212" s="9" t="s">
         <v>86</v>
@@ -14463,9 +14463,9 @@
       </c>
     </row>
     <row r="213" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A213" s="9">
+      <c r="A213" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>205</v>
+        <v>26-60</v>
       </c>
       <c r="B213" s="9" t="s">
         <v>329</v>
@@ -14503,9 +14503,9 @@
       </c>
     </row>
     <row r="214" spans="1:15" s="40" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A214" s="9">
+      <c r="A214" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>206</v>
+        <v>26-61</v>
       </c>
       <c r="B214" s="9" t="s">
         <v>329</v>
@@ -14543,9 +14543,9 @@
       </c>
     </row>
     <row r="215" spans="1:15" s="42" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A215" s="9">
+      <c r="A215" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>207</v>
+        <v>26-62</v>
       </c>
       <c r="B215" s="9" t="s">
         <v>17</v>
@@ -14585,9 +14585,9 @@
       <c r="O215" s="142"/>
     </row>
     <row r="216" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A216" s="9">
+      <c r="A216" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>208</v>
+        <v>26-63</v>
       </c>
       <c r="B216" s="9" t="s">
         <v>329</v>
@@ -14623,9 +14623,9 @@
       <c r="O216" s="142"/>
     </row>
     <row r="217" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A217" s="9">
+      <c r="A217" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>209</v>
+        <v>26-64</v>
       </c>
       <c r="B217" s="9" t="s">
         <v>17</v>
@@ -14665,9 +14665,9 @@
       <c r="O217" s="142"/>
     </row>
     <row r="218" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A218" s="9">
-        <f t="shared" ref="A218:A274" si="4">ROW()-ROW($A$8)</f>
-        <v>210</v>
+      <c r="A218" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>26-65</v>
       </c>
       <c r="B218" s="9" t="s">
         <v>185</v>
@@ -14703,9 +14703,9 @@
       <c r="O218" s="142"/>
     </row>
     <row r="219" spans="1:15" s="25" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A219" s="9">
-        <f t="shared" si="4"/>
-        <v>211</v>
+      <c r="A219" s="9" t="str">
+        <f t="shared" ref="A219:A274" si="4">CONCATENATE("26-",ROW()-ROW($A$153))</f>
+        <v>26-66</v>
       </c>
       <c r="B219" s="9" t="s">
         <v>329</v>
@@ -14741,9 +14741,9 @@
       <c r="O219" s="142"/>
     </row>
     <row r="220" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A220" s="9">
+      <c r="A220" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>212</v>
+        <v>26-67</v>
       </c>
       <c r="B220" s="9" t="s">
         <v>17</v>
@@ -14783,9 +14783,9 @@
       <c r="O220" s="142"/>
     </row>
     <row r="221" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A221" s="9">
+      <c r="A221" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>213</v>
+        <v>26-68</v>
       </c>
       <c r="B221" s="9" t="s">
         <v>329</v>
@@ -14823,9 +14823,9 @@
       <c r="O221" s="142"/>
     </row>
     <row r="222" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A222" s="9">
+      <c r="A222" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>214</v>
+        <v>26-69</v>
       </c>
       <c r="B222" s="9" t="s">
         <v>17</v>
@@ -14869,9 +14869,9 @@
       </c>
     </row>
     <row r="223" spans="1:15" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A223" s="9">
+      <c r="A223" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>215</v>
+        <v>26-70</v>
       </c>
       <c r="B223" s="9" t="s">
         <v>17</v>
@@ -14911,9 +14911,9 @@
       <c r="O223" s="142"/>
     </row>
     <row r="224" spans="1:15" s="19" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A224" s="9">
+      <c r="A224" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>216</v>
+        <v>26-71</v>
       </c>
       <c r="B224" s="9" t="s">
         <v>17</v>
@@ -14955,9 +14955,9 @@
       <c r="O224" s="142"/>
     </row>
     <row r="225" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A225" s="9">
+      <c r="A225" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>217</v>
+        <v>26-72</v>
       </c>
       <c r="B225" s="9" t="s">
         <v>86</v>
@@ -14999,9 +14999,9 @@
       <c r="O225" s="142"/>
     </row>
     <row r="226" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A226" s="9">
+      <c r="A226" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>218</v>
+        <v>26-73</v>
       </c>
       <c r="B226" s="9" t="s">
         <v>239</v>
@@ -15041,9 +15041,9 @@
       <c r="O226" s="178"/>
     </row>
     <row r="227" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A227" s="9">
+      <c r="A227" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>219</v>
+        <v>26-74</v>
       </c>
       <c r="B227" s="9" t="s">
         <v>185</v>
@@ -15081,9 +15081,9 @@
       <c r="O227" s="142"/>
     </row>
     <row r="228" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A228" s="9">
+      <c r="A228" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>220</v>
+        <v>26-75</v>
       </c>
       <c r="B228" s="9" t="s">
         <v>329</v>
@@ -15121,9 +15121,9 @@
       <c r="O228" s="142"/>
     </row>
     <row r="229" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A229" s="9">
+      <c r="A229" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>221</v>
+        <v>26-76</v>
       </c>
       <c r="B229" s="9" t="s">
         <v>86</v>
@@ -15165,9 +15165,9 @@
       <c r="O229" s="142"/>
     </row>
     <row r="230" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A230" s="9">
+      <c r="A230" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>222</v>
+        <v>26-77</v>
       </c>
       <c r="B230" s="9" t="s">
         <v>17</v>
@@ -15209,9 +15209,9 @@
       <c r="O230" s="142"/>
     </row>
     <row r="231" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A231" s="9">
+      <c r="A231" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>223</v>
+        <v>26-78</v>
       </c>
       <c r="B231" s="9" t="s">
         <v>329</v>
@@ -15247,9 +15247,9 @@
       <c r="O231" s="142"/>
     </row>
     <row r="232" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A232" s="9">
+      <c r="A232" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>224</v>
+        <v>26-79</v>
       </c>
       <c r="B232" s="9" t="s">
         <v>329</v>
@@ -15285,9 +15285,9 @@
       <c r="O232" s="142"/>
     </row>
     <row r="233" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A233" s="9">
+      <c r="A233" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>225</v>
+        <v>26-80</v>
       </c>
       <c r="B233" s="9" t="s">
         <v>329</v>
@@ -15323,9 +15323,9 @@
       <c r="O233" s="142"/>
     </row>
     <row r="234" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A234" s="9">
+      <c r="A234" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>226</v>
+        <v>26-81</v>
       </c>
       <c r="B234" s="9" t="s">
         <v>329</v>
@@ -15361,9 +15361,9 @@
       <c r="O234" s="142"/>
     </row>
     <row r="235" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A235" s="9">
+      <c r="A235" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>227</v>
+        <v>26-82</v>
       </c>
       <c r="B235" s="9" t="s">
         <v>86</v>
@@ -15401,9 +15401,9 @@
       <c r="O235" s="142"/>
     </row>
     <row r="236" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A236" s="9">
+      <c r="A236" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>228</v>
+        <v>26-83</v>
       </c>
       <c r="B236" s="9" t="s">
         <v>86</v>
@@ -15441,9 +15441,9 @@
       <c r="O236" s="142"/>
     </row>
     <row r="237" spans="1:15" ht="35.1" customHeight="1">
-      <c r="A237" s="9">
+      <c r="A237" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>229</v>
+        <v>26-84</v>
       </c>
       <c r="B237" s="9" t="s">
         <v>86</v>
@@ -15481,9 +15481,9 @@
       <c r="O237" s="142"/>
     </row>
     <row r="238" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A238" s="9">
+      <c r="A238" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>230</v>
+        <v>26-85</v>
       </c>
       <c r="B238" s="9" t="s">
         <v>86</v>
@@ -15521,9 +15521,9 @@
       <c r="O238" s="142"/>
     </row>
     <row r="239" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A239" s="9">
+      <c r="A239" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>231</v>
+        <v>26-86</v>
       </c>
       <c r="B239" s="9" t="s">
         <v>86</v>
@@ -15561,9 +15561,9 @@
       <c r="O239" s="142"/>
     </row>
     <row r="240" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A240" s="9">
+      <c r="A240" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>232</v>
+        <v>26-87</v>
       </c>
       <c r="B240" s="9" t="s">
         <v>86</v>
@@ -15601,9 +15601,9 @@
       <c r="O240" s="142"/>
     </row>
     <row r="241" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A241" s="9">
+      <c r="A241" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>233</v>
+        <v>26-88</v>
       </c>
       <c r="B241" s="9" t="s">
         <v>86</v>
@@ -15641,9 +15641,9 @@
       <c r="O241" s="142"/>
     </row>
     <row r="242" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A242" s="9">
+      <c r="A242" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>234</v>
+        <v>26-89</v>
       </c>
       <c r="B242" s="9" t="s">
         <v>86</v>
@@ -15681,9 +15681,9 @@
       <c r="O242" s="142"/>
     </row>
     <row r="243" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A243" s="9">
+      <c r="A243" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>235</v>
+        <v>26-90</v>
       </c>
       <c r="B243" s="9" t="s">
         <v>17</v>
@@ -15719,9 +15719,9 @@
       <c r="O243" s="142"/>
     </row>
     <row r="244" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A244" s="9">
+      <c r="A244" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>236</v>
+        <v>26-91</v>
       </c>
       <c r="B244" s="9" t="s">
         <v>17</v>
@@ -15757,9 +15757,9 @@
       <c r="O244" s="142"/>
     </row>
     <row r="245" spans="1:15" s="32" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A245" s="9">
+      <c r="A245" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>237</v>
+        <v>26-92</v>
       </c>
       <c r="B245" s="9" t="s">
         <v>17</v>
@@ -15795,9 +15795,9 @@
       <c r="O245" s="142"/>
     </row>
     <row r="246" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A246" s="9">
+      <c r="A246" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>238</v>
+        <v>26-93</v>
       </c>
       <c r="B246" s="9" t="s">
         <v>17</v>
@@ -15837,9 +15837,9 @@
       <c r="O246" s="142"/>
     </row>
     <row r="247" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A247" s="9">
+      <c r="A247" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>239</v>
+        <v>26-94</v>
       </c>
       <c r="B247" s="9" t="s">
         <v>17</v>
@@ -15879,9 +15879,9 @@
       <c r="O247" s="142"/>
     </row>
     <row r="248" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A248" s="9">
+      <c r="A248" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>240</v>
+        <v>26-95</v>
       </c>
       <c r="B248" s="9" t="s">
         <v>462</v>
@@ -15915,9 +15915,9 @@
       <c r="O248" s="142"/>
     </row>
     <row r="249" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A249" s="9">
+      <c r="A249" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>241</v>
+        <v>26-96</v>
       </c>
       <c r="B249" s="9" t="s">
         <v>462</v>
@@ -15951,9 +15951,9 @@
       <c r="O249" s="142"/>
     </row>
     <row r="250" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A250" s="9">
+      <c r="A250" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>242</v>
+        <v>26-97</v>
       </c>
       <c r="B250" s="9" t="s">
         <v>86</v>
@@ -15991,9 +15991,9 @@
       <c r="O250" s="142"/>
     </row>
     <row r="251" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A251" s="9">
+      <c r="A251" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>243</v>
+        <v>26-98</v>
       </c>
       <c r="B251" s="9" t="s">
         <v>462</v>
@@ -16027,9 +16027,9 @@
       <c r="O251" s="142"/>
     </row>
     <row r="252" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A252" s="9">
+      <c r="A252" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>244</v>
+        <v>26-99</v>
       </c>
       <c r="B252" s="9" t="s">
         <v>462</v>
@@ -16063,9 +16063,9 @@
       <c r="O252" s="142"/>
     </row>
     <row r="253" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A253" s="9">
+      <c r="A253" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>245</v>
+        <v>26-100</v>
       </c>
       <c r="B253" s="9" t="s">
         <v>462</v>
@@ -16099,9 +16099,9 @@
       <c r="O253" s="142"/>
     </row>
     <row r="254" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A254" s="9">
+      <c r="A254" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>246</v>
+        <v>26-101</v>
       </c>
       <c r="B254" s="9" t="s">
         <v>462</v>
@@ -16135,9 +16135,9 @@
       <c r="O254" s="142"/>
     </row>
     <row r="255" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A255" s="9">
+      <c r="A255" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>247</v>
+        <v>26-102</v>
       </c>
       <c r="B255" s="9" t="s">
         <v>462</v>
@@ -16171,9 +16171,9 @@
       <c r="O255" s="142"/>
     </row>
     <row r="256" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A256" s="9">
+      <c r="A256" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>248</v>
+        <v>26-103</v>
       </c>
       <c r="B256" s="9" t="s">
         <v>462</v>
@@ -16207,9 +16207,9 @@
       <c r="O256" s="142"/>
     </row>
     <row r="257" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A257" s="9">
+      <c r="A257" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>249</v>
+        <v>26-104</v>
       </c>
       <c r="B257" s="9" t="s">
         <v>462</v>
@@ -16243,9 +16243,9 @@
       <c r="O257" s="142"/>
     </row>
     <row r="258" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A258" s="9">
+      <c r="A258" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>250</v>
+        <v>26-105</v>
       </c>
       <c r="B258" s="9" t="s">
         <v>462</v>
@@ -16279,9 +16279,9 @@
       <c r="O258" s="142"/>
     </row>
     <row r="259" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A259" s="9">
+      <c r="A259" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>251</v>
+        <v>26-106</v>
       </c>
       <c r="B259" s="9" t="s">
         <v>462</v>
@@ -16315,9 +16315,9 @@
       <c r="O259" s="142"/>
     </row>
     <row r="260" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A260" s="9">
+      <c r="A260" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>252</v>
+        <v>26-107</v>
       </c>
       <c r="B260" s="9" t="s">
         <v>462</v>
@@ -16351,9 +16351,9 @@
       <c r="O260" s="142"/>
     </row>
     <row r="261" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A261" s="9">
+      <c r="A261" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>253</v>
+        <v>26-108</v>
       </c>
       <c r="B261" s="9" t="s">
         <v>462</v>
@@ -16387,9 +16387,9 @@
       <c r="O261" s="142"/>
     </row>
     <row r="262" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A262" s="9">
+      <c r="A262" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>254</v>
+        <v>26-109</v>
       </c>
       <c r="B262" s="9" t="s">
         <v>462</v>
@@ -16423,9 +16423,9 @@
       <c r="O262" s="142"/>
     </row>
     <row r="263" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A263" s="9">
+      <c r="A263" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>255</v>
+        <v>26-110</v>
       </c>
       <c r="B263" s="9" t="s">
         <v>462</v>
@@ -16459,9 +16459,9 @@
       <c r="O263" s="142"/>
     </row>
     <row r="264" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A264" s="9">
+      <c r="A264" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>256</v>
+        <v>26-111</v>
       </c>
       <c r="B264" s="9" t="s">
         <v>462</v>
@@ -16495,9 +16495,9 @@
       <c r="O264" s="142"/>
     </row>
     <row r="265" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A265" s="9">
+      <c r="A265" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>257</v>
+        <v>26-112</v>
       </c>
       <c r="B265" s="9" t="s">
         <v>462</v>
@@ -16531,9 +16531,9 @@
       <c r="O265" s="142"/>
     </row>
     <row r="266" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A266" s="9">
+      <c r="A266" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>258</v>
+        <v>26-113</v>
       </c>
       <c r="B266" s="9" t="s">
         <v>462</v>
@@ -16567,9 +16567,9 @@
       <c r="O266" s="142"/>
     </row>
     <row r="267" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A267" s="9">
+      <c r="A267" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>259</v>
+        <v>26-114</v>
       </c>
       <c r="B267" s="9" t="s">
         <v>462</v>
@@ -16603,9 +16603,9 @@
       <c r="O267" s="142"/>
     </row>
     <row r="268" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A268" s="9">
+      <c r="A268" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>26-115</v>
       </c>
       <c r="B268" s="9" t="s">
         <v>462</v>
@@ -16641,9 +16641,9 @@
       <c r="O268" s="142"/>
     </row>
     <row r="269" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A269" s="9">
+      <c r="A269" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>261</v>
+        <v>26-116</v>
       </c>
       <c r="B269" s="9" t="s">
         <v>462</v>
@@ -16679,9 +16679,9 @@
       <c r="O269" s="142"/>
     </row>
     <row r="270" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A270" s="9">
+      <c r="A270" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>262</v>
+        <v>26-117</v>
       </c>
       <c r="B270" s="9" t="s">
         <v>462</v>
@@ -16717,9 +16717,9 @@
       <c r="O270" s="142"/>
     </row>
     <row r="271" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A271" s="9">
+      <c r="A271" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>263</v>
+        <v>26-118</v>
       </c>
       <c r="B271" s="9" t="s">
         <v>462</v>
@@ -16755,9 +16755,9 @@
       <c r="O271" s="142"/>
     </row>
     <row r="272" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A272" s="9">
+      <c r="A272" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>264</v>
+        <v>26-119</v>
       </c>
       <c r="B272" s="9" t="s">
         <v>462</v>
@@ -16793,9 +16793,9 @@
       <c r="O272" s="142"/>
     </row>
     <row r="273" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A273" s="9">
+      <c r="A273" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>265</v>
+        <v>26-120</v>
       </c>
       <c r="B273" s="9" t="s">
         <v>462</v>
@@ -16831,9 +16831,9 @@
       <c r="O273" s="142"/>
     </row>
     <row r="274" spans="1:15" s="54" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A274" s="9">
+      <c r="A274" s="9" t="str">
         <f t="shared" si="4"/>
-        <v>266</v>
+        <v>26-121</v>
       </c>
       <c r="B274" s="9" t="s">
         <v>462</v>
